--- a/baza.xlsx
+++ b/baza.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Google_brat\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FASTAPI\SHNQ CALCULATSIYA\shnq_adreska\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1D17A0-D17D-4F73-9DAC-8FE6A5C03935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B39B85-0DE8-4E81-9ADD-23D573F47B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1219,7 +1219,9 @@
       <c r="H16" t="s">
         <v>65</v>
       </c>
-      <c r="I16" s="16"/>
+      <c r="I16" s="16">
+        <v>1</v>
+      </c>
       <c r="J16">
         <v>0</v>
       </c>
